--- a/assets/Danh sách phòng.xlsx
+++ b/assets/Danh sách phòng.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30317"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lvdao1\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\btbngoc\Downloads\G2summer2026\G2summer2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{44928667-BA67-4287-96D2-913F587B6205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6D481BF-C917-4F3E-B26A-EFC691E3E3F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{E8AA434A-7375-444A-8C9C-0376E44D2AD5}"/>
+    <workbookView xWindow="28680" yWindow="990" windowWidth="29040" windowHeight="15720" xr2:uid="{E8AA434A-7375-444A-8C9C-0376E44D2AD5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="195">
   <si>
     <t>LDAP</t>
   </si>
@@ -77,9 +75,6 @@
     <t>A3</t>
   </si>
   <si>
-    <t>Đinh Mạnh Thắng, Cà Văn Quế</t>
-  </si>
-  <si>
     <t>dmthang2</t>
   </si>
   <si>
@@ -176,9 +171,6 @@
     <t>A11</t>
   </si>
   <si>
-    <t>Nguyễn Duy Mạnh, Lưu Quang Minh</t>
-  </si>
-  <si>
     <t>lqminh3</t>
   </si>
   <si>
@@ -615,13 +607,25 @@
   </si>
   <si>
     <t>tqtrung2</t>
+  </si>
+  <si>
+    <t>Cà Văn Quế, Lưu Quang Minh</t>
+  </si>
+  <si>
+    <t>Nguyễn Duy Mạnh, Đinh Mạnh Thắng</t>
+  </si>
+  <si>
+    <t>Lưu Quang Minh, Cà Văn Quế</t>
+  </si>
+  <si>
+    <t>Đinh Mạnh Thắng, Nguyễn Duy Mạnh</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -682,7 +686,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -707,6 +711,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="14">
     <border>
@@ -907,7 +917,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -999,6 +1009,11 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1314,7 +1329,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A672F8F-C138-4385-A071-9B8BE506795B}">
   <dimension ref="A1:D95"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" customWidth="1"/>
     <col min="2" max="2" width="19.140625" style="1" customWidth="1"/>
@@ -1322,7 +1337,7 @@
     <col min="4" max="4" width="12.5703125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="2" customFormat="1">
+    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1336,7 +1351,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="43" t="s">
         <v>4</v>
       </c>
@@ -1350,7 +1365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>7</v>
       </c>
@@ -1364,7 +1379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>10</v>
       </c>
@@ -1378,7 +1393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
         <v>11</v>
       </c>
@@ -1386,1241 +1401,1241 @@
         <v>12</v>
       </c>
       <c r="C5" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="D5" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
         <v>13</v>
-      </c>
-      <c r="D5" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="16" t="s">
-        <v>14</v>
       </c>
       <c r="B6" s="17" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>13</v>
+        <v>194</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="C7" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="D7" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="16" t="s">
+      <c r="B8" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="16" t="s">
+      <c r="B9" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="C9" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="D9" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="16" t="s">
+      <c r="B10" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="16" t="s">
+      <c r="B11" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="C11" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="D11" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="16" t="s">
+      <c r="B12" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="16" t="s">
+      <c r="B13" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="C13" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="D13" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="16" t="s">
+      <c r="B14" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="16" t="s">
+      <c r="B15" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="C15" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="D15" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="16" t="s">
+      <c r="B16" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B17" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="20" t="s">
+      <c r="D17" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D17" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="16" t="s">
+      <c r="B18" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="C18" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="D18" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="16" t="s">
+      <c r="B19" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="D19" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="16" t="s">
+      <c r="B20" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="C20" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="D20" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="D20" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="16" t="s">
+      <c r="B21" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D21" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="D21" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="16" t="s">
+      <c r="B22" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="C22" s="51" t="s">
+        <v>192</v>
+      </c>
+      <c r="D22" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="B23" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="D23" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="D22" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="16" t="s">
+      <c r="B24" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="D23" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="21" t="s">
+      <c r="C24" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="D24" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="B25" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D25" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="D24" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="21" t="s">
+      <c r="B26" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="C25" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="D25" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="16" t="s">
+      <c r="C26" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="D26" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="B27" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="D27" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="16" t="s">
+      <c r="B28" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B27" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C27" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="D27" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="16" t="s">
+      <c r="C28" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="D28" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="C28" s="18" t="s">
+      <c r="B29" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D29" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="D28" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="16" t="s">
+      <c r="B30" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="B29" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="C29" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="D29" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="16" t="s">
+      <c r="C30" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="B30" s="17" t="s">
+      <c r="D30" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="C30" s="18" t="s">
+      <c r="B31" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D31" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="D30" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="16" t="s">
+      <c r="B32" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="B31" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="C31" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="D31" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="16" t="s">
+      <c r="C32" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="B32" s="17" t="s">
+      <c r="D32" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="C32" s="18" t="s">
+      <c r="B33" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="D33" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="D32" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="23" t="s">
+      <c r="B34" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="B33" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="C33" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="D33" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="16" t="s">
+      <c r="C34" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="B34" s="17" t="s">
+      <c r="D34" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="C34" s="18" t="s">
+      <c r="B35" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D35" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="D34" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="16" t="s">
+      <c r="B36" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="B35" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C35" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="D35" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="16" t="s">
+      <c r="C36" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="B36" s="17" t="s">
+      <c r="D36" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="C36" s="18" t="s">
+      <c r="B37" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="D37" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="D36" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="16" t="s">
+      <c r="B38" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="B37" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="C37" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="D37" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="16" t="s">
+      <c r="C38" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="B38" s="17" t="s">
+      <c r="D38" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C38" s="18" t="s">
+      <c r="B39" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D39" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="D38" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="7" t="s">
+      <c r="B40" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="B39" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D39" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="16" t="s">
+      <c r="C40" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="B40" s="17" t="s">
+      <c r="D40" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="C40" s="18" t="s">
+      <c r="B41" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="C41" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="D41" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D40" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="16" t="s">
+      <c r="B42" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="B41" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="C41" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="D41" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="7" t="s">
+      <c r="C42" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="B42" s="17" t="s">
+      <c r="D42" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="C42" s="9" t="s">
+      <c r="B43" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="C43" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="D43" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="D42" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="24" t="s">
+      <c r="B44" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="B43" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="C43" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="D43" s="27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="28" t="s">
+      <c r="C44" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="B44" s="29" t="s">
+      <c r="D44" s="31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="C44" s="30" t="s">
+      <c r="B45" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="C45" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="D45" s="35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="D44" s="31">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" s="32" t="s">
+      <c r="B46" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="B45" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="C45" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="D45" s="35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" s="32" t="s">
+      <c r="C46" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="B46" s="33" t="s">
+      <c r="D46" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="C46" s="34" t="s">
+      <c r="B47" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="C47" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="D47" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="D46" s="35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" s="32" t="s">
+      <c r="B48" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="B47" s="33" t="s">
-        <v>93</v>
-      </c>
-      <c r="C47" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="D47" s="35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" s="36" t="s">
+      <c r="C48" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="B48" s="33" t="s">
+      <c r="D48" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="C48" s="34" t="s">
+      <c r="B49" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="C49" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="D49" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="32" t="s">
         <v>98</v>
       </c>
-      <c r="D48" s="35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="A49" s="32" t="s">
+      <c r="B50" s="33" t="s">
         <v>99</v>
       </c>
-      <c r="B49" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="C49" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="D49" s="35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" s="32" t="s">
+      <c r="C50" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="B50" s="33" t="s">
+      <c r="D50" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="C50" s="47" t="s">
+      <c r="B51" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="C51" s="48" t="s">
+        <v>100</v>
+      </c>
+      <c r="D51" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="D50" s="35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" s="32" t="s">
+      <c r="B52" s="33" t="s">
         <v>103</v>
       </c>
-      <c r="B51" s="33" t="s">
-        <v>101</v>
-      </c>
-      <c r="C51" s="48" t="s">
-        <v>102</v>
-      </c>
-      <c r="D51" s="35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="A52" s="32" t="s">
+      <c r="C52" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="B52" s="33" t="s">
+      <c r="D52" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="32" t="s">
         <v>105</v>
       </c>
-      <c r="C52" s="34" t="s">
+      <c r="B53" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="C53" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="D53" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="32" t="s">
         <v>106</v>
       </c>
-      <c r="D52" s="35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
-      <c r="A53" s="32" t="s">
+      <c r="B54" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="B53" s="33" t="s">
-        <v>105</v>
-      </c>
-      <c r="C53" s="34" t="s">
-        <v>106</v>
-      </c>
-      <c r="D53" s="35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
-      <c r="A54" s="32" t="s">
+      <c r="C54" s="34" t="s">
         <v>108</v>
       </c>
-      <c r="B54" s="33" t="s">
+      <c r="D54" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="C54" s="34" t="s">
+      <c r="B55" s="33" t="s">
+        <v>107</v>
+      </c>
+      <c r="C55" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="D55" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="D54" s="35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
-      <c r="A55" s="32" t="s">
+      <c r="B56" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="B55" s="33" t="s">
-        <v>109</v>
-      </c>
-      <c r="C55" s="37" t="s">
-        <v>110</v>
-      </c>
-      <c r="D55" s="35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4">
-      <c r="A56" s="32" t="s">
+      <c r="C56" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="B56" s="33" t="s">
+      <c r="D56" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="C56" s="34" t="s">
+      <c r="B57" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="C57" s="34" t="s">
+        <v>112</v>
+      </c>
+      <c r="D57" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="D56" s="35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57" s="32" t="s">
+      <c r="B58" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="B57" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="C57" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="D57" s="35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
-      <c r="A58" s="32" t="s">
+      <c r="C58" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="B58" s="33" t="s">
+      <c r="D58" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="C58" s="34" t="s">
+      <c r="B59" s="33" t="s">
+        <v>115</v>
+      </c>
+      <c r="C59" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="D59" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="32" t="s">
         <v>118</v>
       </c>
-      <c r="D58" s="35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
-      <c r="A59" s="32" t="s">
+      <c r="B60" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="B59" s="33" t="s">
-        <v>117</v>
-      </c>
-      <c r="C59" s="34" t="s">
-        <v>118</v>
-      </c>
-      <c r="D59" s="35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
-      <c r="A60" s="32" t="s">
+      <c r="C60" s="34" t="s">
         <v>120</v>
       </c>
-      <c r="B60" s="33" t="s">
+      <c r="D60" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="C60" s="34" t="s">
+      <c r="B61" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="C61" s="34" t="s">
+        <v>120</v>
+      </c>
+      <c r="D61" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="D60" s="35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
-      <c r="A61" s="32" t="s">
+      <c r="B62" s="33" t="s">
         <v>123</v>
       </c>
-      <c r="B61" s="33" t="s">
-        <v>121</v>
-      </c>
-      <c r="C61" s="34" t="s">
-        <v>122</v>
-      </c>
-      <c r="D61" s="35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
-      <c r="A62" s="32" t="s">
+      <c r="C62" s="34" t="s">
         <v>124</v>
       </c>
-      <c r="B62" s="33" t="s">
+      <c r="D62" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="C62" s="34" t="s">
+      <c r="B63" s="33" t="s">
+        <v>123</v>
+      </c>
+      <c r="C63" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="D63" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="D62" s="35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="A63" s="32" t="s">
+      <c r="B64" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="B63" s="33" t="s">
-        <v>125</v>
-      </c>
-      <c r="C63" s="34" t="s">
-        <v>126</v>
-      </c>
-      <c r="D63" s="35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64" s="32" t="s">
+      <c r="C64" s="34" t="s">
         <v>128</v>
       </c>
-      <c r="B64" s="33" t="s">
+      <c r="D64" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="C64" s="34" t="s">
+      <c r="B65" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="C65" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="D65" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="32" t="s">
         <v>130</v>
       </c>
-      <c r="D64" s="35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65" s="32" t="s">
+      <c r="B66" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="B65" s="33" t="s">
-        <v>129</v>
-      </c>
-      <c r="C65" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="D65" s="35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="A66" s="32" t="s">
+      <c r="C66" s="34" t="s">
         <v>132</v>
       </c>
-      <c r="B66" s="33" t="s">
+      <c r="D66" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="32" t="s">
         <v>133</v>
       </c>
-      <c r="C66" s="34" t="s">
+      <c r="B67" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="C67" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="D67" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="32" t="s">
         <v>134</v>
       </c>
-      <c r="D66" s="35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67" s="32" t="s">
+      <c r="B68" s="33" t="s">
         <v>135</v>
       </c>
-      <c r="B67" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="C67" s="34" t="s">
-        <v>134</v>
-      </c>
-      <c r="D67" s="35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68" s="32" t="s">
+      <c r="C68" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="B68" s="33" t="s">
+      <c r="D68" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="32" t="s">
         <v>137</v>
       </c>
-      <c r="C68" s="34" t="s">
+      <c r="B69" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="C69" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="D69" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="D68" s="35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69" s="32" t="s">
+      <c r="B70" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="B69" s="33" t="s">
-        <v>137</v>
-      </c>
-      <c r="C69" s="34" t="s">
-        <v>138</v>
-      </c>
-      <c r="D69" s="35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
-      <c r="A70" s="32" t="s">
+      <c r="C70" s="34" t="s">
         <v>140</v>
       </c>
-      <c r="B70" s="33" t="s">
+      <c r="D70" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="32" t="s">
         <v>141</v>
       </c>
-      <c r="C70" s="34" t="s">
+      <c r="B71" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="D70" s="35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
-      <c r="A71" s="32" t="s">
+      <c r="C71" s="34" t="s">
         <v>143</v>
       </c>
-      <c r="B71" s="33" t="s">
+      <c r="D71" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="C71" s="34" t="s">
+      <c r="B72" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="C72" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="D72" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="D71" s="35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4">
-      <c r="A72" s="32" t="s">
+      <c r="B73" s="33" t="s">
         <v>146</v>
       </c>
-      <c r="B72" s="33" t="s">
-        <v>144</v>
-      </c>
-      <c r="C72" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="D72" s="35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4">
-      <c r="A73" s="32" t="s">
+      <c r="C73" s="34" t="s">
         <v>147</v>
       </c>
-      <c r="B73" s="33" t="s">
+      <c r="D73" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="32" t="s">
         <v>148</v>
       </c>
-      <c r="C73" s="34" t="s">
+      <c r="B74" s="33" t="s">
+        <v>146</v>
+      </c>
+      <c r="C74" s="34" t="s">
+        <v>147</v>
+      </c>
+      <c r="D74" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="D73" s="35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4">
-      <c r="A74" s="32" t="s">
+      <c r="B75" s="33" t="s">
         <v>150</v>
       </c>
-      <c r="B74" s="33" t="s">
-        <v>148</v>
-      </c>
-      <c r="C74" s="34" t="s">
-        <v>149</v>
-      </c>
-      <c r="D74" s="35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4">
-      <c r="A75" s="32" t="s">
+      <c r="C75" s="34" t="s">
         <v>151</v>
       </c>
-      <c r="B75" s="33" t="s">
+      <c r="D75" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="38" t="s">
         <v>152</v>
       </c>
-      <c r="C75" s="34" t="s">
+      <c r="B76" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="C76" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="D76" s="41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="D75" s="35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4">
-      <c r="A76" s="38" t="s">
+      <c r="B77" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="B76" s="39" t="s">
-        <v>152</v>
-      </c>
-      <c r="C76" s="40" t="s">
-        <v>153</v>
-      </c>
-      <c r="D76" s="41">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4">
-      <c r="A77" s="4" t="s">
+      <c r="C77" s="6" t="s">
         <v>155</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="C77" s="6" t="s">
-        <v>157</v>
       </c>
       <c r="D77" s="42">
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:4">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D78" s="10">
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="1:4">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C79" s="9" t="s">
         <v>159</v>
-      </c>
-      <c r="B79" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="C79" s="9" t="s">
-        <v>161</v>
       </c>
       <c r="D79" s="10">
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:4">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="11" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D80" s="10">
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:4">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="C81" s="9" t="s">
         <v>163</v>
-      </c>
-      <c r="B81" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="C81" s="9" t="s">
-        <v>165</v>
       </c>
       <c r="D81" s="10">
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="1:4">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D82" s="10">
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:4">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="C83" s="9" t="s">
         <v>167</v>
-      </c>
-      <c r="B83" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="C83" s="9" t="s">
-        <v>169</v>
       </c>
       <c r="D83" s="10">
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:4">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D84" s="10">
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:4">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="C85" s="9" t="s">
         <v>171</v>
-      </c>
-      <c r="B85" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="C85" s="9" t="s">
-        <v>173</v>
       </c>
       <c r="D85" s="10">
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:4">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D86" s="10">
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="1:4">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="C87" s="9" t="s">
         <v>175</v>
-      </c>
-      <c r="B87" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="C87" s="9" t="s">
-        <v>177</v>
       </c>
       <c r="D87" s="10">
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:4">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D88" s="10">
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="1:4">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="B89" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="C89" s="9" t="s">
         <v>179</v>
-      </c>
-      <c r="B89" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="C89" s="9" t="s">
-        <v>181</v>
       </c>
       <c r="D89" s="10">
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="1:4">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="B90" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="C90" s="9" t="s">
         <v>182</v>
-      </c>
-      <c r="B90" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="C90" s="9" t="s">
-        <v>184</v>
       </c>
       <c r="D90" s="10">
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="1:4">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="B91" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C91" s="9" t="s">
         <v>185</v>
-      </c>
-      <c r="B91" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="C91" s="9" t="s">
-        <v>187</v>
       </c>
       <c r="D91" s="10">
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:4">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="B92" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="C92" s="14" t="s">
         <v>188</v>
-      </c>
-      <c r="B92" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="C92" s="14" t="s">
-        <v>190</v>
       </c>
       <c r="D92" s="15">
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="1:4">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B94" s="8"/>
       <c r="C94" s="9"/>
       <c r="D94" s="10"/>
     </row>
-    <row r="95" spans="1:4">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B95" s="8"/>
       <c r="C95" s="9"/>

--- a/assets/Danh sách phòng.xlsx
+++ b/assets/Danh sách phòng.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\btbngoc\Downloads\G2summer2026\G2summer2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6D481BF-C917-4F3E-B26A-EFC691E3E3F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F9619A3-B910-45BD-A1B4-2897CD4BFB06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="990" windowWidth="29040" windowHeight="15720" xr2:uid="{E8AA434A-7375-444A-8C9C-0376E44D2AD5}"/>
+    <workbookView xWindow="2730" yWindow="2655" windowWidth="21600" windowHeight="11295" xr2:uid="{E8AA434A-7375-444A-8C9C-0376E44D2AD5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1332,1314 +1332,1314 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="2" max="2" width="19.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" style="1" customWidth="1"/>
     <col min="3" max="3" width="53.5703125" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="2" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="44" t="s">
-        <v>5</v>
+      <c r="B2" s="46">
+        <v>1</v>
       </c>
       <c r="C2" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="46">
-        <v>1</v>
+      <c r="D2" s="44" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="17" t="s">
-        <v>8</v>
+      <c r="B3" s="19">
+        <v>1</v>
       </c>
       <c r="C3" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="19">
-        <v>1</v>
+      <c r="D3" s="17" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="17" t="s">
-        <v>8</v>
+      <c r="B4" s="19">
+        <v>1</v>
       </c>
       <c r="C4" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="19">
-        <v>1</v>
+      <c r="D4" s="17" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="17" t="s">
-        <v>12</v>
+      <c r="B5" s="19">
+        <v>1</v>
       </c>
       <c r="C5" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="D5" s="19">
-        <v>1</v>
+      <c r="D5" s="17" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="17" t="s">
-        <v>12</v>
+      <c r="B6" s="19">
+        <v>1</v>
       </c>
       <c r="C6" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="D6" s="19">
-        <v>1</v>
+      <c r="D6" s="17" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="17" t="s">
-        <v>15</v>
+      <c r="B7" s="19">
+        <v>1</v>
       </c>
       <c r="C7" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="19">
-        <v>1</v>
+      <c r="D7" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="17" t="s">
-        <v>15</v>
+      <c r="B8" s="19">
+        <v>1</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="19">
-        <v>1</v>
+      <c r="D8" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="17" t="s">
-        <v>19</v>
+      <c r="B9" s="19">
+        <v>1</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="19">
-        <v>1</v>
+      <c r="D9" s="17" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="17" t="s">
-        <v>19</v>
+      <c r="B10" s="19">
+        <v>1</v>
       </c>
       <c r="C10" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="19">
-        <v>1</v>
+      <c r="D10" s="17" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="17" t="s">
-        <v>23</v>
+      <c r="B11" s="19">
+        <v>1</v>
       </c>
       <c r="C11" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="19">
-        <v>1</v>
+      <c r="D11" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="17" t="s">
-        <v>23</v>
+      <c r="B12" s="19">
+        <v>1</v>
       </c>
       <c r="C12" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="19">
-        <v>1</v>
+      <c r="D12" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="17" t="s">
-        <v>27</v>
+      <c r="B13" s="19">
+        <v>1</v>
       </c>
       <c r="C13" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="19">
-        <v>1</v>
+      <c r="D13" s="17" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="17" t="s">
-        <v>27</v>
+      <c r="B14" s="19">
+        <v>1</v>
       </c>
       <c r="C14" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="19">
-        <v>1</v>
+      <c r="D14" s="17" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="17" t="s">
-        <v>31</v>
+      <c r="B15" s="19">
+        <v>1</v>
       </c>
       <c r="C15" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="19">
-        <v>1</v>
+      <c r="D15" s="17" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="17" t="s">
-        <v>31</v>
+      <c r="B16" s="19">
+        <v>1</v>
       </c>
       <c r="C16" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="19">
-        <v>1</v>
+      <c r="D16" s="17" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="17" t="s">
-        <v>31</v>
+      <c r="B17" s="19">
+        <v>1</v>
       </c>
       <c r="C17" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="19">
-        <v>1</v>
+      <c r="D17" s="17" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="17" t="s">
-        <v>36</v>
+      <c r="B18" s="19">
+        <v>1</v>
       </c>
       <c r="C18" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="19">
-        <v>1</v>
+      <c r="D18" s="17" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="17" t="s">
-        <v>36</v>
+      <c r="B19" s="19">
+        <v>1</v>
       </c>
       <c r="C19" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="19">
-        <v>1</v>
+      <c r="D19" s="17" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="17" t="s">
-        <v>40</v>
+      <c r="B20" s="19">
+        <v>1</v>
       </c>
       <c r="C20" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="19">
-        <v>1</v>
+      <c r="D20" s="17" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="17" t="s">
-        <v>40</v>
+      <c r="B21" s="19">
+        <v>1</v>
       </c>
       <c r="C21" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="19">
-        <v>1</v>
+      <c r="D21" s="17" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="50" t="s">
-        <v>44</v>
+      <c r="B22" s="19">
+        <v>1</v>
       </c>
       <c r="C22" s="51" t="s">
         <v>192</v>
       </c>
-      <c r="D22" s="19">
-        <v>1</v>
+      <c r="D22" s="50" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B23" s="17" t="s">
-        <v>44</v>
+      <c r="B23" s="19">
+        <v>1</v>
       </c>
       <c r="C23" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="D23" s="19">
-        <v>1</v>
+      <c r="D23" s="17" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="17" t="s">
-        <v>47</v>
+      <c r="B24" s="19">
+        <v>1</v>
       </c>
       <c r="C24" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="D24" s="19">
-        <v>1</v>
+      <c r="D24" s="17" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="17" t="s">
-        <v>47</v>
+      <c r="B25" s="19">
+        <v>1</v>
       </c>
       <c r="C25" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="D25" s="19">
-        <v>1</v>
+      <c r="D25" s="17" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="17" t="s">
-        <v>51</v>
+      <c r="B26" s="19">
+        <v>1</v>
       </c>
       <c r="C26" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D26" s="19">
-        <v>1</v>
+      <c r="D26" s="17" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="17" t="s">
-        <v>51</v>
+      <c r="B27" s="19">
+        <v>1</v>
       </c>
       <c r="C27" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="D27" s="19">
-        <v>1</v>
+      <c r="D27" s="17" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="17" t="s">
-        <v>55</v>
+      <c r="B28" s="19">
+        <v>1</v>
       </c>
       <c r="C28" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D28" s="19">
-        <v>1</v>
+      <c r="D28" s="17" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B29" s="17" t="s">
-        <v>55</v>
+      <c r="B29" s="19">
+        <v>1</v>
       </c>
       <c r="C29" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D29" s="19">
-        <v>1</v>
+      <c r="D29" s="17" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="17" t="s">
-        <v>59</v>
+      <c r="B30" s="19">
+        <v>1</v>
       </c>
       <c r="C30" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="D30" s="19">
-        <v>1</v>
+      <c r="D30" s="17" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="B31" s="17" t="s">
-        <v>59</v>
+      <c r="B31" s="19">
+        <v>1</v>
       </c>
       <c r="C31" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="D31" s="19">
-        <v>1</v>
+      <c r="D31" s="17" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="17" t="s">
-        <v>63</v>
+      <c r="B32" s="19">
+        <v>1</v>
       </c>
       <c r="C32" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D32" s="19">
-        <v>1</v>
+      <c r="D32" s="17" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="B33" s="17" t="s">
-        <v>63</v>
+      <c r="B33" s="19">
+        <v>1</v>
       </c>
       <c r="C33" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D33" s="19">
-        <v>1</v>
+      <c r="D33" s="17" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="B34" s="17" t="s">
-        <v>67</v>
+      <c r="B34" s="19">
+        <v>1</v>
       </c>
       <c r="C34" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D34" s="19">
-        <v>1</v>
+      <c r="D34" s="17" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="B35" s="17" t="s">
-        <v>67</v>
+      <c r="B35" s="19">
+        <v>1</v>
       </c>
       <c r="C35" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D35" s="19">
-        <v>1</v>
+      <c r="D35" s="17" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="17" t="s">
-        <v>71</v>
+      <c r="B36" s="19">
+        <v>1</v>
       </c>
       <c r="C36" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D36" s="19">
-        <v>1</v>
+      <c r="D36" s="17" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="B37" s="17" t="s">
-        <v>71</v>
+      <c r="B37" s="19">
+        <v>1</v>
       </c>
       <c r="C37" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D37" s="19">
-        <v>1</v>
+      <c r="D37" s="17" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="B38" s="17" t="s">
-        <v>75</v>
+      <c r="B38" s="19">
+        <v>1</v>
       </c>
       <c r="C38" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D38" s="19">
-        <v>1</v>
+      <c r="D38" s="17" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B39" s="8" t="s">
-        <v>75</v>
+      <c r="B39" s="19">
+        <v>1</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D39" s="19">
-        <v>1</v>
+      <c r="D39" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="B40" s="17" t="s">
-        <v>79</v>
+      <c r="B40" s="19">
+        <v>1</v>
       </c>
       <c r="C40" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="D40" s="19">
-        <v>1</v>
+      <c r="D40" s="17" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="B41" s="17" t="s">
-        <v>79</v>
+      <c r="B41" s="19">
+        <v>1</v>
       </c>
       <c r="C41" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="D41" s="19">
-        <v>1</v>
+      <c r="D41" s="17" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B42" s="17" t="s">
-        <v>83</v>
+      <c r="B42" s="19">
+        <v>1</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D42" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D42" s="17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="B43" s="25" t="s">
-        <v>83</v>
+      <c r="B43" s="27">
+        <v>1</v>
       </c>
       <c r="C43" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="D43" s="27">
-        <v>1</v>
+      <c r="D43" s="25" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="B44" s="29" t="s">
-        <v>87</v>
+      <c r="B44" s="31">
+        <v>2</v>
       </c>
       <c r="C44" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="D44" s="31">
-        <v>2</v>
+      <c r="D44" s="29" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="B45" s="33" t="s">
-        <v>87</v>
+      <c r="B45" s="35">
+        <v>1</v>
       </c>
       <c r="C45" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="D45" s="35">
-        <v>1</v>
+      <c r="D45" s="33" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="B46" s="33" t="s">
-        <v>91</v>
+      <c r="B46" s="35">
+        <v>2</v>
       </c>
       <c r="C46" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="D46" s="35">
-        <v>2</v>
+      <c r="D46" s="33" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="B47" s="33" t="s">
-        <v>91</v>
+      <c r="B47" s="35">
+        <v>2</v>
       </c>
       <c r="C47" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="D47" s="35">
-        <v>2</v>
+      <c r="D47" s="33" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="B48" s="33" t="s">
-        <v>95</v>
+      <c r="B48" s="35">
+        <v>2</v>
       </c>
       <c r="C48" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="D48" s="35">
-        <v>2</v>
+      <c r="D48" s="33" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="B49" s="33" t="s">
-        <v>95</v>
+      <c r="B49" s="35">
+        <v>2</v>
       </c>
       <c r="C49" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="D49" s="35">
-        <v>2</v>
+      <c r="D49" s="33" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="32" t="s">
         <v>98</v>
       </c>
-      <c r="B50" s="33" t="s">
-        <v>99</v>
+      <c r="B50" s="35">
+        <v>2</v>
       </c>
       <c r="C50" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="D50" s="35">
-        <v>2</v>
+      <c r="D50" s="33" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="B51" s="33" t="s">
-        <v>99</v>
+      <c r="B51" s="35">
+        <v>2</v>
       </c>
       <c r="C51" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="D51" s="35">
-        <v>2</v>
+      <c r="D51" s="33" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="B52" s="33" t="s">
-        <v>103</v>
+      <c r="B52" s="35">
+        <v>2</v>
       </c>
       <c r="C52" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="D52" s="35">
-        <v>2</v>
+      <c r="D52" s="33" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="32" t="s">
         <v>105</v>
       </c>
-      <c r="B53" s="33" t="s">
-        <v>103</v>
+      <c r="B53" s="35">
+        <v>2</v>
       </c>
       <c r="C53" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="D53" s="35">
-        <v>2</v>
+      <c r="D53" s="33" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="32" t="s">
         <v>106</v>
       </c>
-      <c r="B54" s="33" t="s">
-        <v>107</v>
+      <c r="B54" s="35">
+        <v>2</v>
       </c>
       <c r="C54" s="34" t="s">
         <v>108</v>
       </c>
-      <c r="D54" s="35">
-        <v>2</v>
+      <c r="D54" s="33" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="B55" s="33" t="s">
-        <v>107</v>
+      <c r="B55" s="35">
+        <v>2</v>
       </c>
       <c r="C55" s="37" t="s">
         <v>108</v>
       </c>
-      <c r="D55" s="35">
-        <v>2</v>
+      <c r="D55" s="33" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="B56" s="33" t="s">
-        <v>111</v>
+      <c r="B56" s="35">
+        <v>2</v>
       </c>
       <c r="C56" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="D56" s="35">
-        <v>2</v>
+      <c r="D56" s="33" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="B57" s="33" t="s">
-        <v>111</v>
+      <c r="B57" s="35">
+        <v>2</v>
       </c>
       <c r="C57" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="D57" s="35">
-        <v>2</v>
+      <c r="D57" s="33" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="B58" s="33" t="s">
-        <v>115</v>
+      <c r="B58" s="35">
+        <v>2</v>
       </c>
       <c r="C58" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="D58" s="35">
-        <v>2</v>
+      <c r="D58" s="33" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="B59" s="33" t="s">
-        <v>115</v>
+      <c r="B59" s="35">
+        <v>2</v>
       </c>
       <c r="C59" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="D59" s="35">
-        <v>2</v>
+      <c r="D59" s="33" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="32" t="s">
         <v>118</v>
       </c>
-      <c r="B60" s="33" t="s">
-        <v>119</v>
+      <c r="B60" s="35">
+        <v>2</v>
       </c>
       <c r="C60" s="34" t="s">
         <v>120</v>
       </c>
-      <c r="D60" s="35">
-        <v>2</v>
+      <c r="D60" s="33" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="B61" s="33" t="s">
-        <v>119</v>
+      <c r="B61" s="35">
+        <v>2</v>
       </c>
       <c r="C61" s="34" t="s">
         <v>120</v>
       </c>
-      <c r="D61" s="35">
-        <v>2</v>
+      <c r="D61" s="33" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="B62" s="33" t="s">
-        <v>123</v>
+      <c r="B62" s="35">
+        <v>2</v>
       </c>
       <c r="C62" s="34" t="s">
         <v>124</v>
       </c>
-      <c r="D62" s="35">
-        <v>2</v>
+      <c r="D62" s="33" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="B63" s="33" t="s">
-        <v>123</v>
+      <c r="B63" s="35">
+        <v>2</v>
       </c>
       <c r="C63" s="34" t="s">
         <v>124</v>
       </c>
-      <c r="D63" s="35">
-        <v>2</v>
+      <c r="D63" s="33" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="B64" s="33" t="s">
-        <v>127</v>
+      <c r="B64" s="35">
+        <v>2</v>
       </c>
       <c r="C64" s="34" t="s">
         <v>128</v>
       </c>
-      <c r="D64" s="35">
-        <v>2</v>
+      <c r="D64" s="33" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="B65" s="33" t="s">
-        <v>127</v>
+      <c r="B65" s="35">
+        <v>2</v>
       </c>
       <c r="C65" s="34" t="s">
         <v>128</v>
       </c>
-      <c r="D65" s="35">
-        <v>2</v>
+      <c r="D65" s="33" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="32" t="s">
         <v>130</v>
       </c>
-      <c r="B66" s="33" t="s">
-        <v>131</v>
+      <c r="B66" s="35">
+        <v>2</v>
       </c>
       <c r="C66" s="34" t="s">
         <v>132</v>
       </c>
-      <c r="D66" s="35">
-        <v>2</v>
+      <c r="D66" s="33" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="32" t="s">
         <v>133</v>
       </c>
-      <c r="B67" s="33" t="s">
-        <v>131</v>
+      <c r="B67" s="35">
+        <v>2</v>
       </c>
       <c r="C67" s="34" t="s">
         <v>132</v>
       </c>
-      <c r="D67" s="35">
-        <v>2</v>
+      <c r="D67" s="33" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="32" t="s">
         <v>134</v>
       </c>
-      <c r="B68" s="33" t="s">
-        <v>135</v>
+      <c r="B68" s="35">
+        <v>2</v>
       </c>
       <c r="C68" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="D68" s="35">
-        <v>2</v>
+      <c r="D68" s="33" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="32" t="s">
         <v>137</v>
       </c>
-      <c r="B69" s="33" t="s">
-        <v>135</v>
+      <c r="B69" s="35">
+        <v>2</v>
       </c>
       <c r="C69" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="D69" s="35">
-        <v>2</v>
+      <c r="D69" s="33" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="B70" s="33" t="s">
-        <v>139</v>
+      <c r="B70" s="35">
+        <v>2</v>
       </c>
       <c r="C70" s="34" t="s">
         <v>140</v>
       </c>
-      <c r="D70" s="35">
-        <v>2</v>
+      <c r="D70" s="33" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="32" t="s">
         <v>141</v>
       </c>
-      <c r="B71" s="33" t="s">
-        <v>142</v>
+      <c r="B71" s="35">
+        <v>2</v>
       </c>
       <c r="C71" s="34" t="s">
         <v>143</v>
       </c>
-      <c r="D71" s="35">
-        <v>2</v>
+      <c r="D71" s="33" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="B72" s="33" t="s">
-        <v>142</v>
+      <c r="B72" s="35">
+        <v>2</v>
       </c>
       <c r="C72" s="34" t="s">
         <v>143</v>
       </c>
-      <c r="D72" s="35">
-        <v>2</v>
+      <c r="D72" s="33" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="B73" s="33" t="s">
-        <v>146</v>
+      <c r="B73" s="35">
+        <v>2</v>
       </c>
       <c r="C73" s="34" t="s">
         <v>147</v>
       </c>
-      <c r="D73" s="35">
-        <v>2</v>
+      <c r="D73" s="33" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="32" t="s">
         <v>148</v>
       </c>
-      <c r="B74" s="33" t="s">
-        <v>146</v>
+      <c r="B74" s="35">
+        <v>2</v>
       </c>
       <c r="C74" s="34" t="s">
         <v>147</v>
       </c>
-      <c r="D74" s="35">
-        <v>2</v>
+      <c r="D74" s="33" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="B75" s="33" t="s">
-        <v>150</v>
+      <c r="B75" s="35">
+        <v>2</v>
       </c>
       <c r="C75" s="34" t="s">
         <v>151</v>
       </c>
-      <c r="D75" s="35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D75" s="33" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="38" t="s">
         <v>152</v>
       </c>
-      <c r="B76" s="39" t="s">
-        <v>150</v>
+      <c r="B76" s="41">
+        <v>2</v>
       </c>
       <c r="C76" s="40" t="s">
         <v>151</v>
       </c>
-      <c r="D76" s="41">
-        <v>2</v>
+      <c r="D76" s="39" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="B77" s="5" t="s">
-        <v>154</v>
+      <c r="B77" s="42">
+        <v>3</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="D77" s="42">
-        <v>3</v>
+      <c r="D77" s="5" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="B78" s="8" t="s">
-        <v>154</v>
+      <c r="B78" s="10">
+        <v>3</v>
       </c>
       <c r="C78" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="D78" s="10">
-        <v>3</v>
+      <c r="D78" s="8" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="B79" s="8" t="s">
-        <v>158</v>
+      <c r="B79" s="10">
+        <v>3</v>
       </c>
       <c r="C79" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="D79" s="10">
-        <v>3</v>
+      <c r="D79" s="8" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="B80" s="8" t="s">
-        <v>158</v>
+      <c r="B80" s="10">
+        <v>3</v>
       </c>
       <c r="C80" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="D80" s="10">
-        <v>3</v>
+      <c r="D80" s="8" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="B81" s="8" t="s">
-        <v>162</v>
+      <c r="B81" s="10">
+        <v>3</v>
       </c>
       <c r="C81" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="D81" s="10">
-        <v>3</v>
+      <c r="D81" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="B82" s="8" t="s">
-        <v>162</v>
+      <c r="B82" s="10">
+        <v>3</v>
       </c>
       <c r="C82" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="D82" s="10">
-        <v>3</v>
+      <c r="D82" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="B83" s="8" t="s">
-        <v>166</v>
+      <c r="B83" s="10">
+        <v>3</v>
       </c>
       <c r="C83" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="D83" s="10">
-        <v>3</v>
+      <c r="D83" s="8" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="B84" s="8" t="s">
-        <v>166</v>
+      <c r="B84" s="10">
+        <v>3</v>
       </c>
       <c r="C84" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="D84" s="10">
-        <v>3</v>
+      <c r="D84" s="8" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="B85" s="8" t="s">
-        <v>170</v>
+      <c r="B85" s="10">
+        <v>3</v>
       </c>
       <c r="C85" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="D85" s="10">
-        <v>3</v>
+      <c r="D85" s="8" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="B86" s="8" t="s">
-        <v>170</v>
+      <c r="B86" s="10">
+        <v>3</v>
       </c>
       <c r="C86" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="D86" s="10">
-        <v>3</v>
+      <c r="D86" s="8" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="B87" s="8" t="s">
-        <v>174</v>
+      <c r="B87" s="10">
+        <v>3</v>
       </c>
       <c r="C87" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="D87" s="10">
-        <v>3</v>
+      <c r="D87" s="8" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="B88" s="8" t="s">
-        <v>174</v>
+      <c r="B88" s="10">
+        <v>3</v>
       </c>
       <c r="C88" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="D88" s="10">
-        <v>3</v>
+      <c r="D88" s="8" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="B89" s="8" t="s">
-        <v>178</v>
+      <c r="B89" s="10">
+        <v>3</v>
       </c>
       <c r="C89" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="D89" s="10">
-        <v>3</v>
+      <c r="D89" s="8" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="B90" s="8" t="s">
-        <v>181</v>
+      <c r="B90" s="10">
+        <v>3</v>
       </c>
       <c r="C90" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="D90" s="10">
-        <v>3</v>
+      <c r="D90" s="8" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="B91" s="8" t="s">
-        <v>184</v>
+      <c r="B91" s="10">
+        <v>3</v>
       </c>
       <c r="C91" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="D91" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D91" s="8" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="B92" s="13" t="s">
-        <v>187</v>
+      <c r="B92" s="15">
+        <v>3</v>
       </c>
       <c r="C92" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="D92" s="15">
-        <v>3</v>
+      <c r="D92" s="13" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="B94" s="8"/>
+      <c r="B94" s="10"/>
       <c r="C94" s="9"/>
-      <c r="D94" s="10"/>
+      <c r="D94" s="8"/>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="B95" s="8"/>
+      <c r="B95" s="10"/>
       <c r="C95" s="9"/>
-      <c r="D95" s="10"/>
+      <c r="D95" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/assets/Danh sách phòng.xlsx
+++ b/assets/Danh sách phòng.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\btbngoc\Downloads\G2summer2026\G2summer2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F9619A3-B910-45BD-A1B4-2897CD4BFB06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A49C0D3C-5C22-41A6-92D1-A004DF1DA63C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2655" windowWidth="21600" windowHeight="11295" xr2:uid="{E8AA434A-7375-444A-8C9C-0376E44D2AD5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E8AA434A-7375-444A-8C9C-0376E44D2AD5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="191">
   <si>
     <t>LDAP</t>
   </si>
@@ -48,15 +48,6 @@
     <t>Xe</t>
   </si>
   <si>
-    <t>vhdung1</t>
-  </si>
-  <si>
-    <t>A1</t>
-  </si>
-  <si>
-    <t>Vũ Hồng Dũng</t>
-  </si>
-  <si>
     <t>hvan</t>
   </si>
   <si>
@@ -76,9 +67,6 @@
   </si>
   <si>
     <t>dmthang2</t>
-  </si>
-  <si>
-    <t>ldquan</t>
   </si>
   <si>
     <t>A4</t>
@@ -625,7 +613,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -665,14 +653,6 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <strike/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -917,7 +897,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -999,16 +979,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1328,7 +1300,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A672F8F-C138-4385-A071-9B8BE506795B}">
-  <dimension ref="A1:D95"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" customWidth="1"/>
@@ -1337,7 +1309,7 @@
     <col min="4" max="4" width="19.140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="2" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1352,16 +1324,16 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="46">
-        <v>1</v>
-      </c>
-      <c r="C2" s="45" t="s">
+      <c r="B2" s="19">
+        <v>1</v>
+      </c>
+      <c r="C2" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="44" t="s">
+      <c r="D2" s="17" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1373,38 +1345,38 @@
         <v>1</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" s="19">
         <v>1</v>
       </c>
       <c r="C4" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="D4" s="17" t="s">
         <v>9</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="B5" s="19">
         <v>1</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1415,10 +1387,10 @@
         <v>1</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>194</v>
+        <v>12</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1534,45 +1506,45 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="20" t="s">
         <v>30</v>
       </c>
       <c r="B15" s="19">
         <v>1</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="19">
+        <v>1</v>
+      </c>
+      <c r="C16" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="19">
-        <v>1</v>
-      </c>
-      <c r="C16" s="18" t="s">
+      <c r="D16" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="17" t="s">
-        <v>31</v>
-      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="16" t="s">
         <v>34</v>
       </c>
       <c r="B17" s="19">
         <v>1</v>
       </c>
       <c r="C17" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="17" t="s">
         <v>32</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1605,62 +1577,62 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="B20" s="19">
         <v>1</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>41</v>
+        <v>190</v>
       </c>
       <c r="D20" s="17" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="19">
+        <v>1</v>
+      </c>
+      <c r="C21" s="47" t="s">
+        <v>188</v>
+      </c>
+      <c r="D21" s="46" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="19">
-        <v>1</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="49" t="s">
+      <c r="B22" s="19">
+        <v>1</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="19">
-        <v>1</v>
-      </c>
-      <c r="C22" s="51" t="s">
-        <v>192</v>
-      </c>
-      <c r="D22" s="50" t="s">
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="19">
+        <v>1</v>
+      </c>
+      <c r="C23" s="18" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="B23" s="19">
-        <v>1</v>
-      </c>
-      <c r="C23" s="18" t="s">
-        <v>191</v>
-      </c>
       <c r="D23" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="21" t="s">
+      <c r="A24" s="16" t="s">
         <v>46</v>
       </c>
       <c r="B24" s="19">
@@ -1674,13 +1646,13 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="21" t="s">
+      <c r="A25" s="16" t="s">
         <v>49</v>
       </c>
       <c r="B25" s="19">
         <v>1</v>
       </c>
-      <c r="C25" s="18" t="s">
+      <c r="C25" s="22" t="s">
         <v>48</v>
       </c>
       <c r="D25" s="17" t="s">
@@ -1708,7 +1680,7 @@
       <c r="B27" s="19">
         <v>1</v>
       </c>
-      <c r="C27" s="22" t="s">
+      <c r="C27" s="18" t="s">
         <v>52</v>
       </c>
       <c r="D27" s="17" t="s">
@@ -1758,7 +1730,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="16" t="s">
+      <c r="A31" s="23" t="s">
         <v>61</v>
       </c>
       <c r="B31" s="19">
@@ -1786,7 +1758,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="23" t="s">
+      <c r="A33" s="16" t="s">
         <v>65</v>
       </c>
       <c r="B33" s="19">
@@ -1842,16 +1814,16 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="16" t="s">
+      <c r="A37" s="7" t="s">
         <v>73</v>
       </c>
       <c r="B37" s="19">
         <v>1</v>
       </c>
-      <c r="C37" s="18" t="s">
+      <c r="C37" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D37" s="17" t="s">
+      <c r="D37" s="8" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1870,86 +1842,86 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="7" t="s">
+      <c r="A39" s="16" t="s">
         <v>77</v>
       </c>
       <c r="B39" s="19">
         <v>1</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="C39" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D39" s="8" t="s">
+      <c r="D39" s="17" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="16" t="s">
+      <c r="A40" s="7" t="s">
         <v>78</v>
       </c>
       <c r="B40" s="19">
         <v>1</v>
       </c>
-      <c r="C40" s="18" t="s">
+      <c r="C40" s="9" t="s">
         <v>80</v>
       </c>
       <c r="D40" s="17" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="16" t="s">
+    <row r="41" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="B41" s="19">
-        <v>1</v>
-      </c>
-      <c r="C41" s="18" t="s">
+      <c r="B41" s="27">
+        <v>1</v>
+      </c>
+      <c r="C41" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="D41" s="17" t="s">
+      <c r="D41" s="25" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="7" t="s">
+      <c r="A42" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="B42" s="19">
-        <v>1</v>
-      </c>
-      <c r="C42" s="9" t="s">
+      <c r="B42" s="31">
+        <v>2</v>
+      </c>
+      <c r="C42" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="D42" s="17" t="s">
+      <c r="D42" s="29" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="24" t="s">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="B43" s="27">
-        <v>1</v>
-      </c>
-      <c r="C43" s="26" t="s">
+      <c r="B43" s="35">
+        <v>1</v>
+      </c>
+      <c r="C43" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="D43" s="25" t="s">
+      <c r="D43" s="33" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="28" t="s">
+      <c r="A44" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="B44" s="31">
-        <v>2</v>
-      </c>
-      <c r="C44" s="30" t="s">
+      <c r="B44" s="35">
+        <v>2</v>
+      </c>
+      <c r="C44" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="D44" s="29" t="s">
+      <c r="D44" s="33" t="s">
         <v>87</v>
       </c>
     </row>
@@ -1958,7 +1930,7 @@
         <v>89</v>
       </c>
       <c r="B45" s="35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C45" s="34" t="s">
         <v>88</v>
@@ -1968,7 +1940,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="32" t="s">
+      <c r="A46" s="36" t="s">
         <v>90</v>
       </c>
       <c r="B46" s="35">
@@ -1996,13 +1968,13 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="36" t="s">
+      <c r="A48" s="32" t="s">
         <v>94</v>
       </c>
       <c r="B48" s="35">
         <v>2</v>
       </c>
-      <c r="C48" s="34" t="s">
+      <c r="C48" s="43" t="s">
         <v>96</v>
       </c>
       <c r="D48" s="33" t="s">
@@ -2016,7 +1988,7 @@
       <c r="B49" s="35">
         <v>2</v>
       </c>
-      <c r="C49" s="34" t="s">
+      <c r="C49" s="44" t="s">
         <v>96</v>
       </c>
       <c r="D49" s="33" t="s">
@@ -2030,7 +2002,7 @@
       <c r="B50" s="35">
         <v>2</v>
       </c>
-      <c r="C50" s="47" t="s">
+      <c r="C50" s="34" t="s">
         <v>100</v>
       </c>
       <c r="D50" s="33" t="s">
@@ -2044,7 +2016,7 @@
       <c r="B51" s="35">
         <v>2</v>
       </c>
-      <c r="C51" s="48" t="s">
+      <c r="C51" s="34" t="s">
         <v>100</v>
       </c>
       <c r="D51" s="33" t="s">
@@ -2072,7 +2044,7 @@
       <c r="B53" s="35">
         <v>2</v>
       </c>
-      <c r="C53" s="34" t="s">
+      <c r="C53" s="37" t="s">
         <v>104</v>
       </c>
       <c r="D53" s="33" t="s">
@@ -2100,7 +2072,7 @@
       <c r="B55" s="35">
         <v>2</v>
       </c>
-      <c r="C55" s="37" t="s">
+      <c r="C55" s="34" t="s">
         <v>108</v>
       </c>
       <c r="D55" s="33" t="s">
@@ -2297,24 +2269,24 @@
         <v>2</v>
       </c>
       <c r="C69" s="34" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D69" s="33" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="B70" s="35">
+        <v>2</v>
+      </c>
+      <c r="C70" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="D70" s="33" t="s">
         <v>138</v>
-      </c>
-      <c r="B70" s="35">
-        <v>2</v>
-      </c>
-      <c r="C70" s="34" t="s">
-        <v>140</v>
-      </c>
-      <c r="D70" s="33" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -2359,64 +2331,64 @@
         <v>146</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="32" t="s">
+    <row r="74" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="38" t="s">
         <v>148</v>
       </c>
-      <c r="B74" s="35">
-        <v>2</v>
-      </c>
-      <c r="C74" s="34" t="s">
+      <c r="B74" s="41">
+        <v>2</v>
+      </c>
+      <c r="C74" s="40" t="s">
         <v>147</v>
       </c>
-      <c r="D74" s="33" t="s">
+      <c r="D74" s="39" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="32" t="s">
+      <c r="A75" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B75" s="35">
-        <v>2</v>
-      </c>
-      <c r="C75" s="34" t="s">
+      <c r="B75" s="42">
+        <v>3</v>
+      </c>
+      <c r="C75" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="D75" s="33" t="s">
+      <c r="D75" s="5" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="38" t="s">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="B76" s="41">
-        <v>2</v>
-      </c>
-      <c r="C76" s="40" t="s">
+      <c r="B76" s="10">
+        <v>3</v>
+      </c>
+      <c r="C76" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="D76" s="39" t="s">
+      <c r="D76" s="8" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="4" t="s">
+      <c r="A77" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="B77" s="42">
+      <c r="B77" s="10">
         <v>3</v>
       </c>
-      <c r="C77" s="6" t="s">
+      <c r="C77" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="D77" s="5" t="s">
+      <c r="D77" s="8" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="7" t="s">
+      <c r="A78" s="11" t="s">
         <v>156</v>
       </c>
       <c r="B78" s="10">
@@ -2444,7 +2416,7 @@
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="11" t="s">
+      <c r="A80" s="7" t="s">
         <v>160</v>
       </c>
       <c r="B80" s="10">
@@ -2563,83 +2535,55 @@
         <v>3</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B89" s="10">
         <v>3</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="B90" s="10">
+    </row>
+    <row r="90" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="B90" s="15">
         <v>3</v>
       </c>
-      <c r="C90" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="D90" s="8" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" s="7" t="s">
+      <c r="C90" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="D90" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="B91" s="10">
-        <v>3</v>
-      </c>
-      <c r="C91" s="9" t="s">
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="D91" s="8" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="12" t="s">
+      <c r="B92" s="10"/>
+      <c r="C92" s="9"/>
+      <c r="D92" s="8"/>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="B92" s="15">
-        <v>3</v>
-      </c>
-      <c r="C92" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="D92" s="13" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="B94" s="10"/>
-      <c r="C94" s="9"/>
-      <c r="D94" s="8"/>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="B95" s="10"/>
-      <c r="C95" s="9"/>
-      <c r="D95" s="8"/>
+      <c r="B93" s="10"/>
+      <c r="C93" s="9"/>
+      <c r="D93" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
